--- a/DataTables/DetailText/剧情/004_04辞别老师.xlsx
+++ b/DataTables/DetailText/剧情/004_04辞别老师.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB63D62F-0CFA-4B77-9F7C-2FC83F02D17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727E9541-B11E-4A53-BEA7-B5FEC4A1E4D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -843,9 +843,7 @@
       <c r="O2" s="24"/>
       <c r="P2" s="24"/>
       <c r="Q2" s="24"/>
-      <c r="R2" s="25">
-        <v>5</v>
-      </c>
+      <c r="R2" s="25"/>
       <c r="S2" s="1" t="b">
         <v>1</v>
       </c>
